--- a/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartZoneConfig@s.xlsx
+++ b/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>#</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>路由区</t>
+  </si>
+  <si>
+    <t>ET1000</t>
+  </si>
+  <si>
+    <t>账号登录服</t>
   </si>
 </sst>
 </file>
@@ -1070,22 +1076,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="C2:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.6283185840708" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.6272727272727" style="3" customWidth="1"/>
     <col min="4" max="7" width="21" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="13.5" spans="7:7">
+    <row r="2" spans="7:7">
       <c r="G2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:7">
+    <row r="3" ht="13.5" spans="3:7">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1102,7 +1108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:7">
+    <row r="4" ht="13.5" spans="3:7">
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1119,7 +1125,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="3:7">
+    <row r="5" ht="13.5" spans="3:7">
       <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
@@ -1177,6 +1183,23 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7">
+      <c r="C9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartZoneConfig@s.xlsx
+++ b/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartZoneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="StartZoneConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>#</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>游戏区</t>
+  </si>
+  <si>
+    <t>ET2</t>
   </si>
   <si>
     <t>机器人区</t>
@@ -1077,11 +1080,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C2:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.1272727272727" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.7545454545455" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.6272727272727" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.7583333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="3" customWidth="1"/>
     <col min="4" max="7" width="21" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
@@ -1091,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="13.5" spans="3:7">
+    <row r="3" spans="3:7">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1108,7 +1111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:7">
+    <row r="4" spans="3:7">
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1125,7 +1128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:7">
+    <row r="5" spans="3:7">
       <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
@@ -1166,10 +1169,14 @@
       <c r="D7" s="5">
         <v>2</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G7" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="3:7">
@@ -1182,7 +1189,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="3:7">
@@ -1196,10 +1203,10 @@
         <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
